--- a/artfynd/A 31789-2020 artfynd.xlsx
+++ b/artfynd/A 31789-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31789-2020 artfynd.xlsx
+++ b/artfynd/A 31789-2020 artfynd.xlsx
@@ -7475,10 +7475,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120076655</v>
+        <v>120058782</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7491,37 +7491,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503418</v>
+        <v>503368</v>
       </c>
       <c r="R62" t="n">
         <v>7134688</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7545,12 +7545,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7577,10 +7577,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120076607</v>
+        <v>120076683</v>
       </c>
       <c r="B63" t="n">
-        <v>79608</v>
+        <v>12337</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7589,25 +7589,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>101283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503455</v>
+        <v>503379</v>
       </c>
       <c r="R63" t="n">
-        <v>7134770</v>
+        <v>7134700</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7653,6 +7653,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7679,10 +7684,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120076603</v>
+        <v>120076655</v>
       </c>
       <c r="B64" t="n">
-        <v>91886</v>
+        <v>78526</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7691,25 +7696,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>232140</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7719,7 +7724,7 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503326</v>
+        <v>503418</v>
       </c>
       <c r="R64" t="n">
         <v>7134688</v>
@@ -7755,11 +7760,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning, under tallåga</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7786,10 +7786,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120058782</v>
+        <v>120076607</v>
       </c>
       <c r="B65" t="n">
-        <v>78263</v>
+        <v>79608</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7802,37 +7802,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503368</v>
+        <v>503455</v>
       </c>
       <c r="R65" t="n">
-        <v>7134688</v>
+        <v>7134770</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7856,12 +7856,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7888,10 +7888,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120076683</v>
+        <v>120076679</v>
       </c>
       <c r="B66" t="n">
-        <v>12337</v>
+        <v>91840</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7900,25 +7900,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>101283</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503379</v>
+        <v>503320</v>
       </c>
       <c r="R66" t="n">
-        <v>7134700</v>
+        <v>7134688</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7964,11 +7964,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7995,10 +7990,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076679</v>
+        <v>120076603</v>
       </c>
       <c r="B67" t="n">
-        <v>91840</v>
+        <v>91886</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8007,25 +8002,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8035,7 +8030,7 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503320</v>
+        <v>503326</v>
       </c>
       <c r="R67" t="n">
         <v>7134688</v>
@@ -8071,6 +8066,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning, under tallåga</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 31789-2020 artfynd.xlsx
+++ b/artfynd/A 31789-2020 artfynd.xlsx
@@ -7475,10 +7475,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120058782</v>
+        <v>120076607</v>
       </c>
       <c r="B62" t="n">
-        <v>78263</v>
+        <v>79608</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7491,37 +7491,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503368</v>
+        <v>503455</v>
       </c>
       <c r="R62" t="n">
-        <v>7134688</v>
+        <v>7134770</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7545,12 +7545,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7577,10 +7577,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120076683</v>
+        <v>120076678</v>
       </c>
       <c r="B63" t="n">
-        <v>12337</v>
+        <v>91840</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7589,25 +7589,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>101283</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503379</v>
+        <v>503396</v>
       </c>
       <c r="R63" t="n">
         <v>7134700</v>
@@ -7653,11 +7653,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7684,10 +7679,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120076655</v>
+        <v>120076679</v>
       </c>
       <c r="B64" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7696,25 +7691,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7724,7 +7719,7 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503418</v>
+        <v>503320</v>
       </c>
       <c r="R64" t="n">
         <v>7134688</v>
@@ -7786,10 +7781,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120076607</v>
+        <v>120076603</v>
       </c>
       <c r="B65" t="n">
-        <v>79608</v>
+        <v>91886</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7798,25 +7793,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>232140</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7826,10 +7821,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503455</v>
+        <v>503326</v>
       </c>
       <c r="R65" t="n">
-        <v>7134770</v>
+        <v>7134688</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7862,6 +7857,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning, under tallåga</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7888,10 +7888,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120076679</v>
+        <v>120076655</v>
       </c>
       <c r="B66" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7900,25 +7900,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503320</v>
+        <v>503418</v>
       </c>
       <c r="R66" t="n">
         <v>7134688</v>
@@ -7990,10 +7990,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076603</v>
+        <v>120058782</v>
       </c>
       <c r="B67" t="n">
-        <v>91886</v>
+        <v>78263</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8002,41 +8002,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>232140</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503326</v>
+        <v>503368</v>
       </c>
       <c r="R67" t="n">
         <v>7134688</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8060,17 +8060,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning, under tallåga</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8097,10 +8092,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120076678</v>
+        <v>120076683</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>12337</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8109,25 +8104,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>101283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8137,7 +8132,7 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503396</v>
+        <v>503379</v>
       </c>
       <c r="R68" t="n">
         <v>7134700</v>
@@ -8173,6 +8168,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 31789-2020 artfynd.xlsx
+++ b/artfynd/A 31789-2020 artfynd.xlsx
@@ -7475,10 +7475,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120076607</v>
+        <v>120076679</v>
       </c>
       <c r="B62" t="n">
-        <v>79608</v>
+        <v>91840</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7487,25 +7487,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7515,10 +7515,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503455</v>
+        <v>503320</v>
       </c>
       <c r="R62" t="n">
-        <v>7134770</v>
+        <v>7134688</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7577,10 +7577,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120076678</v>
+        <v>120076607</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>79608</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7589,25 +7589,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503396</v>
+        <v>503455</v>
       </c>
       <c r="R63" t="n">
-        <v>7134700</v>
+        <v>7134770</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7679,7 +7679,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120076679</v>
+        <v>120076678</v>
       </c>
       <c r="B64" t="n">
         <v>91840</v>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503320</v>
+        <v>503396</v>
       </c>
       <c r="R64" t="n">
-        <v>7134688</v>
+        <v>7134700</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7990,10 +7990,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120058782</v>
+        <v>120076683</v>
       </c>
       <c r="B67" t="n">
-        <v>78263</v>
+        <v>12337</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8002,41 +8002,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>101283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503368</v>
+        <v>503379</v>
       </c>
       <c r="R67" t="n">
-        <v>7134688</v>
+        <v>7134700</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8060,12 +8060,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8092,10 +8097,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120076683</v>
+        <v>120058782</v>
       </c>
       <c r="B68" t="n">
-        <v>12337</v>
+        <v>78263</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8104,41 +8109,44 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>101283</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sönner-Storåhöjden, Jmt</t>
+          <t>Sönner-Storåhöjden, Sönner-Storåhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503379</v>
+        <v>503368</v>
       </c>
       <c r="R68" t="n">
-        <v>7134700</v>
+        <v>7134688</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8170,17 +8178,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31789-2020 artfynd.xlsx
+++ b/artfynd/A 31789-2020 artfynd.xlsx
@@ -7478,7 +7478,7 @@
         <v>120076679</v>
       </c>
       <c r="B62" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7577,10 +7577,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120076607</v>
+        <v>120076683</v>
       </c>
       <c r="B63" t="n">
-        <v>79608</v>
+        <v>12337</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7589,25 +7589,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>101283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503455</v>
+        <v>503379</v>
       </c>
       <c r="R63" t="n">
-        <v>7134770</v>
+        <v>7134700</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7653,6 +7653,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7679,10 +7684,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120076678</v>
+        <v>120076607</v>
       </c>
       <c r="B64" t="n">
-        <v>91840</v>
+        <v>79624</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7691,25 +7696,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7719,10 +7724,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503396</v>
+        <v>503455</v>
       </c>
       <c r="R64" t="n">
-        <v>7134700</v>
+        <v>7134770</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7781,10 +7786,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120076603</v>
+        <v>120076655</v>
       </c>
       <c r="B65" t="n">
-        <v>91886</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7793,25 +7798,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>232140</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7821,7 +7826,7 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503326</v>
+        <v>503418</v>
       </c>
       <c r="R65" t="n">
         <v>7134688</v>
@@ -7857,11 +7862,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning, under tallåga</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7888,10 +7888,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120076655</v>
+        <v>120076603</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>91904</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7900,25 +7900,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>232140</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503418</v>
+        <v>503326</v>
       </c>
       <c r="R66" t="n">
         <v>7134688</v>
@@ -7964,6 +7964,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning, under tallåga</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7990,10 +7995,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076683</v>
+        <v>120076678</v>
       </c>
       <c r="B67" t="n">
-        <v>12337</v>
+        <v>91858</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8002,25 +8007,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>101283</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8030,7 +8035,7 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503379</v>
+        <v>503396</v>
       </c>
       <c r="R67" t="n">
         <v>7134700</v>
@@ -8066,11 +8071,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8100,7 +8100,7 @@
         <v>120058782</v>
       </c>
       <c r="B68" t="n">
-        <v>78263</v>
+        <v>78279</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>

--- a/artfynd/A 31789-2020 artfynd.xlsx
+++ b/artfynd/A 31789-2020 artfynd.xlsx
@@ -7475,10 +7475,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120076679</v>
+        <v>120076683</v>
       </c>
       <c r="B62" t="n">
-        <v>91858</v>
+        <v>12337</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7487,25 +7487,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>101283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7515,10 +7515,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503320</v>
+        <v>503379</v>
       </c>
       <c r="R62" t="n">
-        <v>7134688</v>
+        <v>7134700</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7551,6 +7551,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7577,10 +7582,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120076683</v>
+        <v>120076678</v>
       </c>
       <c r="B63" t="n">
-        <v>12337</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7589,25 +7594,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>101283</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7617,7 +7622,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503379</v>
+        <v>503396</v>
       </c>
       <c r="R63" t="n">
         <v>7134700</v>
@@ -7653,11 +7658,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7786,10 +7786,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120076655</v>
+        <v>120076679</v>
       </c>
       <c r="B65" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7798,25 +7798,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7826,7 +7826,7 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503418</v>
+        <v>503320</v>
       </c>
       <c r="R65" t="n">
         <v>7134688</v>
@@ -7995,10 +7995,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076678</v>
+        <v>120076655</v>
       </c>
       <c r="B67" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8007,25 +8007,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8035,10 +8035,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503396</v>
+        <v>503418</v>
       </c>
       <c r="R67" t="n">
-        <v>7134700</v>
+        <v>7134688</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>

--- a/artfynd/A 31789-2020 artfynd.xlsx
+++ b/artfynd/A 31789-2020 artfynd.xlsx
@@ -7475,10 +7475,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120076683</v>
+        <v>120076655</v>
       </c>
       <c r="B62" t="n">
-        <v>12337</v>
+        <v>78542</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7487,25 +7487,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>101283</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7515,10 +7515,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503379</v>
+        <v>503418</v>
       </c>
       <c r="R62" t="n">
-        <v>7134700</v>
+        <v>7134688</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7551,11 +7551,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7582,10 +7577,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120076678</v>
+        <v>120076603</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>91904</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7594,25 +7589,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7622,10 +7617,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503396</v>
+        <v>503326</v>
       </c>
       <c r="R63" t="n">
-        <v>7134700</v>
+        <v>7134688</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7658,6 +7653,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning, under tallåga</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7684,10 +7684,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120076607</v>
+        <v>120076678</v>
       </c>
       <c r="B64" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7696,25 +7696,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7724,10 +7724,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503455</v>
+        <v>503396</v>
       </c>
       <c r="R64" t="n">
-        <v>7134770</v>
+        <v>7134700</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7888,10 +7888,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120076603</v>
+        <v>120076683</v>
       </c>
       <c r="B66" t="n">
-        <v>91904</v>
+        <v>12337</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7900,25 +7900,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>232140</v>
+        <v>101283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503326</v>
+        <v>503379</v>
       </c>
       <c r="R66" t="n">
-        <v>7134688</v>
+        <v>7134700</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Osäker artbestämning, under tallåga</t>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7995,10 +7995,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076655</v>
+        <v>120076607</v>
       </c>
       <c r="B67" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8011,21 +8011,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8035,10 +8035,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503418</v>
+        <v>503455</v>
       </c>
       <c r="R67" t="n">
-        <v>7134688</v>
+        <v>7134770</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>

--- a/artfynd/A 31789-2020 artfynd.xlsx
+++ b/artfynd/A 31789-2020 artfynd.xlsx
@@ -7475,10 +7475,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120076655</v>
+        <v>120076607</v>
       </c>
       <c r="B62" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7491,21 +7491,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7515,10 +7515,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503418</v>
+        <v>503455</v>
       </c>
       <c r="R62" t="n">
-        <v>7134688</v>
+        <v>7134770</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7577,10 +7577,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120076603</v>
+        <v>120076679</v>
       </c>
       <c r="B63" t="n">
-        <v>91904</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7589,25 +7589,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503326</v>
+        <v>503320</v>
       </c>
       <c r="R63" t="n">
         <v>7134688</v>
@@ -7653,11 +7653,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning, under tallåga</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7786,10 +7781,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120076679</v>
+        <v>120076603</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
+        <v>91904</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7798,25 +7793,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7826,7 +7821,7 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503320</v>
+        <v>503326</v>
       </c>
       <c r="R65" t="n">
         <v>7134688</v>
@@ -7862,6 +7857,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning, under tallåga</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7995,10 +7995,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076607</v>
+        <v>120076655</v>
       </c>
       <c r="B67" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8011,21 +8011,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8035,10 +8035,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503455</v>
+        <v>503418</v>
       </c>
       <c r="R67" t="n">
-        <v>7134770</v>
+        <v>7134688</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>

--- a/artfynd/A 31789-2020 artfynd.xlsx
+++ b/artfynd/A 31789-2020 artfynd.xlsx
@@ -7475,10 +7475,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120076607</v>
+        <v>120076679</v>
       </c>
       <c r="B62" t="n">
-        <v>79624</v>
+        <v>91858</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7487,25 +7487,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7515,10 +7515,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503455</v>
+        <v>503320</v>
       </c>
       <c r="R62" t="n">
-        <v>7134770</v>
+        <v>7134688</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7577,10 +7577,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120076679</v>
+        <v>120076655</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7589,25 +7589,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503320</v>
+        <v>503418</v>
       </c>
       <c r="R63" t="n">
         <v>7134688</v>
@@ -7679,10 +7679,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120076678</v>
+        <v>120076683</v>
       </c>
       <c r="B64" t="n">
-        <v>91858</v>
+        <v>12337</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7691,25 +7691,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>101283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503396</v>
+        <v>503379</v>
       </c>
       <c r="R64" t="n">
         <v>7134700</v>
@@ -7755,6 +7755,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7781,10 +7786,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120076603</v>
+        <v>120076678</v>
       </c>
       <c r="B65" t="n">
-        <v>91904</v>
+        <v>91858</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7793,25 +7798,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7821,10 +7826,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503326</v>
+        <v>503396</v>
       </c>
       <c r="R65" t="n">
-        <v>7134688</v>
+        <v>7134700</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7857,11 +7862,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning, under tallåga</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7888,10 +7888,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120076683</v>
+        <v>120076607</v>
       </c>
       <c r="B66" t="n">
-        <v>12337</v>
+        <v>79624</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7900,25 +7900,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>101283</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503379</v>
+        <v>503455</v>
       </c>
       <c r="R66" t="n">
-        <v>7134700</v>
+        <v>7134770</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7964,11 +7964,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7995,10 +7990,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076655</v>
+        <v>120076603</v>
       </c>
       <c r="B67" t="n">
-        <v>78542</v>
+        <v>91904</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8007,25 +8002,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>232140</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8035,7 +8030,7 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503418</v>
+        <v>503326</v>
       </c>
       <c r="R67" t="n">
         <v>7134688</v>
@@ -8071,6 +8066,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning, under tallåga</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 31789-2020 artfynd.xlsx
+++ b/artfynd/A 31789-2020 artfynd.xlsx
@@ -7475,10 +7475,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120076679</v>
+        <v>120076655</v>
       </c>
       <c r="B62" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7487,25 +7487,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503320</v>
+        <v>503418</v>
       </c>
       <c r="R62" t="n">
         <v>7134688</v>
@@ -7577,10 +7577,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120076655</v>
+        <v>120076679</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7589,25 +7589,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503418</v>
+        <v>503320</v>
       </c>
       <c r="R63" t="n">
         <v>7134688</v>
@@ -7679,10 +7679,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120076683</v>
+        <v>120076678</v>
       </c>
       <c r="B64" t="n">
-        <v>12337</v>
+        <v>91858</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7691,25 +7691,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>101283</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503379</v>
+        <v>503396</v>
       </c>
       <c r="R64" t="n">
         <v>7134700</v>
@@ -7755,11 +7755,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7786,10 +7781,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120076678</v>
+        <v>120076683</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
+        <v>12337</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7798,25 +7793,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>101283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7826,7 +7821,7 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503396</v>
+        <v>503379</v>
       </c>
       <c r="R65" t="n">
         <v>7134700</v>
@@ -7862,6 +7857,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Kläckhål på björkhögstubbe med levande fnösktickor</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7888,10 +7888,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120076607</v>
+        <v>120076603</v>
       </c>
       <c r="B66" t="n">
-        <v>79624</v>
+        <v>91904</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7900,25 +7900,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>232140</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503455</v>
+        <v>503326</v>
       </c>
       <c r="R66" t="n">
-        <v>7134770</v>
+        <v>7134688</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7964,6 +7964,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning, under tallåga</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7990,10 +7995,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076603</v>
+        <v>120076607</v>
       </c>
       <c r="B67" t="n">
-        <v>91904</v>
+        <v>79624</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8002,25 +8007,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>232140</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8030,10 +8035,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503326</v>
+        <v>503455</v>
       </c>
       <c r="R67" t="n">
-        <v>7134688</v>
+        <v>7134770</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8066,11 +8071,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning, under tallåga</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 31789-2020 artfynd.xlsx
+++ b/artfynd/A 31789-2020 artfynd.xlsx
@@ -7475,10 +7475,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120076655</v>
+        <v>120076678</v>
       </c>
       <c r="B62" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7487,25 +7487,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7515,10 +7515,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503418</v>
+        <v>503396</v>
       </c>
       <c r="R62" t="n">
-        <v>7134688</v>
+        <v>7134700</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7577,10 +7577,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120076679</v>
+        <v>120076607</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>79624</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7589,25 +7589,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503320</v>
+        <v>503455</v>
       </c>
       <c r="R63" t="n">
-        <v>7134688</v>
+        <v>7134770</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7679,7 +7679,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120076678</v>
+        <v>120076679</v>
       </c>
       <c r="B64" t="n">
         <v>91858</v>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503396</v>
+        <v>503320</v>
       </c>
       <c r="R64" t="n">
-        <v>7134700</v>
+        <v>7134688</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7995,10 +7995,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120076607</v>
+        <v>120076655</v>
       </c>
       <c r="B67" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8011,21 +8011,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8035,10 +8035,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503455</v>
+        <v>503418</v>
       </c>
       <c r="R67" t="n">
-        <v>7134770</v>
+        <v>7134688</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>

--- a/artfynd/A 31789-2020 artfynd.xlsx
+++ b/artfynd/A 31789-2020 artfynd.xlsx
@@ -8203,10 +8203,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122753578</v>
+        <v>122753582</v>
       </c>
       <c r="B69" t="n">
-        <v>78499</v>
+        <v>78503</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8239,14 +8239,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Abborrtj. NÖ, Jmt</t>
+          <t>Lill-Huvudtj. N, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503266</v>
+        <v>503389</v>
       </c>
       <c r="R69" t="n">
-        <v>7134788</v>
+        <v>7134870</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8309,10 +8309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122753582</v>
+        <v>122753578</v>
       </c>
       <c r="B70" t="n">
-        <v>78499</v>
+        <v>78503</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8345,14 +8345,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lill-Huvudtj. N, Jmt</t>
+          <t>Abborrtj. NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503389</v>
+        <v>503266</v>
       </c>
       <c r="R70" t="n">
-        <v>7134870</v>
+        <v>7134788</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 31789-2020 artfynd.xlsx
+++ b/artfynd/A 31789-2020 artfynd.xlsx
@@ -8203,7 +8203,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122753582</v>
+        <v>122753578</v>
       </c>
       <c r="B69" t="n">
         <v>78503</v>
@@ -8239,14 +8239,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lill-Huvudtj. N, Jmt</t>
+          <t>Abborrtj. NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503389</v>
+        <v>503266</v>
       </c>
       <c r="R69" t="n">
-        <v>7134870</v>
+        <v>7134788</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8309,7 +8309,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122753578</v>
+        <v>122753582</v>
       </c>
       <c r="B70" t="n">
         <v>78503</v>
@@ -8345,14 +8345,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Abborrtj. NÖ, Jmt</t>
+          <t>Lill-Huvudtj. N, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503266</v>
+        <v>503389</v>
       </c>
       <c r="R70" t="n">
-        <v>7134788</v>
+        <v>7134870</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 31789-2020 artfynd.xlsx
+++ b/artfynd/A 31789-2020 artfynd.xlsx
@@ -8203,7 +8203,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122753578</v>
+        <v>122753582</v>
       </c>
       <c r="B69" t="n">
         <v>78503</v>
@@ -8239,14 +8239,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Abborrtj. NÖ, Jmt</t>
+          <t>Lill-Huvudtj. N, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503266</v>
+        <v>503389</v>
       </c>
       <c r="R69" t="n">
-        <v>7134788</v>
+        <v>7134870</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8309,7 +8309,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122753582</v>
+        <v>122753578</v>
       </c>
       <c r="B70" t="n">
         <v>78503</v>
@@ -8345,14 +8345,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lill-Huvudtj. N, Jmt</t>
+          <t>Abborrtj. NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503389</v>
+        <v>503266</v>
       </c>
       <c r="R70" t="n">
-        <v>7134870</v>
+        <v>7134788</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 31789-2020 artfynd.xlsx
+++ b/artfynd/A 31789-2020 artfynd.xlsx
@@ -8206,7 +8206,7 @@
         <v>122753582</v>
       </c>
       <c r="B69" t="n">
-        <v>78503</v>
+        <v>78506</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>122753578</v>
       </c>
       <c r="B70" t="n">
-        <v>78503</v>
+        <v>78506</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>

--- a/artfynd/A 31789-2020 artfynd.xlsx
+++ b/artfynd/A 31789-2020 artfynd.xlsx
@@ -8203,10 +8203,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122753582</v>
+        <v>122753578</v>
       </c>
       <c r="B69" t="n">
-        <v>78506</v>
+        <v>78508</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8239,14 +8239,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lill-Huvudtj. N, Jmt</t>
+          <t>Abborrtj. NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503389</v>
+        <v>503266</v>
       </c>
       <c r="R69" t="n">
-        <v>7134870</v>
+        <v>7134788</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8309,10 +8309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122753578</v>
+        <v>122753582</v>
       </c>
       <c r="B70" t="n">
-        <v>78506</v>
+        <v>78508</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8345,14 +8345,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Abborrtj. NÖ, Jmt</t>
+          <t>Lill-Huvudtj. N, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503266</v>
+        <v>503389</v>
       </c>
       <c r="R70" t="n">
-        <v>7134788</v>
+        <v>7134870</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
